--- a/docs/bobot_kesulitan_modul_fprs_v3.xlsx
+++ b/docs/bobot_kesulitan_modul_fprs_v3.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Semua Modul" sheetId="1" r:id="rId1"/>
@@ -397,7 +397,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,6 +439,12 @@
         <fgColor rgb="FFFFEBEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -467,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -541,6 +547,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2295,55 +2314,55 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="10">
+    <row r="6" spans="1:8" s="37" customFormat="1">
+      <c r="A6" s="33">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
+      <c r="D6" s="35">
+        <v>1</v>
+      </c>
+      <c r="E6" s="36">
         <v>46255</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="36">
         <v>46260</v>
       </c>
-      <c r="G6" s="10">
-        <v>3</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="G6" s="33">
+        <v>3</v>
+      </c>
+      <c r="H6" s="34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="10">
+    <row r="7" spans="1:8" s="37" customFormat="1">
+      <c r="A7" s="33">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="12">
-        <v>3</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="D7" s="35">
+        <v>3</v>
+      </c>
+      <c r="E7" s="36">
         <v>46261</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="36">
         <v>46267</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="33">
         <v>5</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="34" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2451,55 +2470,55 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="10">
+    <row r="12" spans="1:8" s="37" customFormat="1">
+      <c r="A12" s="33">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="12">
-        <v>1</v>
-      </c>
-      <c r="E12" s="25">
+      <c r="D12" s="35">
+        <v>1</v>
+      </c>
+      <c r="E12" s="36">
         <v>46283</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="36">
         <v>46283</v>
       </c>
-      <c r="G12" s="10">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="s">
+      <c r="G12" s="33">
+        <v>1</v>
+      </c>
+      <c r="H12" s="34" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="10">
+    <row r="13" spans="1:8" s="37" customFormat="1">
+      <c r="A13" s="33">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="12">
-        <v>1</v>
-      </c>
-      <c r="E13" s="25">
+      <c r="D13" s="35">
+        <v>1</v>
+      </c>
+      <c r="E13" s="36">
         <v>46286</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="36">
         <v>46288</v>
       </c>
-      <c r="G13" s="10">
-        <v>3</v>
-      </c>
-      <c r="H13" s="11" t="s">
+      <c r="G13" s="33">
+        <v>3</v>
+      </c>
+      <c r="H13" s="34" t="s">
         <v>55</v>
       </c>
     </row>
